--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_34_R4.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_34_R4.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1791</v>
+        <v>4.4157</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0629</v>
+        <v>4.5347</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1162</v>
+        <v>-0.1191</v>
       </c>
       <c r="G2" t="n">
         <v>5.9576</v>
@@ -610,13 +610,13 @@
         <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5979</v>
+        <v>0.8344</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2671</v>
+        <v>0.2047</v>
       </c>
       <c r="U2" t="n">
-        <v>0.865</v>
+        <v>0.6297</v>
       </c>
       <c r="V2" t="n">
         <v>-2.1444</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.868</v>
+        <v>3.4304</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.3412</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2909</v>
+        <v>3.0892</v>
       </c>
       <c r="G3" t="n">
         <v>1.9514</v>
@@ -688,13 +688,13 @@
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0763</v>
+        <v>0.6387</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2715</v>
+        <v>0.0356</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8048</v>
+        <v>0.6032</v>
       </c>
       <c r="V3" t="n">
         <v>1.0722</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.738</v>
+        <v>2.6537</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0706</v>
+        <v>1.9527</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6674</v>
+        <v>0.701</v>
       </c>
       <c r="G4" t="n">
         <v>0.9272</v>
@@ -766,13 +766,13 @@
         <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1507</v>
+        <v>-0.235</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1687</v>
+        <v>-0.2867</v>
       </c>
       <c r="U4" t="n">
-        <v>0.018</v>
+        <v>0.0516</v>
       </c>
       <c r="V4" t="n">
         <v>1.4975</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. VEZENKOV</t>
+          <t>K. PAPANIKOLAOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.723</v>
+        <v>0.4381</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8612</v>
+        <v>-0.3469</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5842</v>
+        <v>0.7851</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.9722</v>
+        <v>2.0283</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0061</v>
+        <v>1.2788</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.9783</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9504</v>
+        <v>1.1347</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7093</v>
+        <v>0.1176</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.6597</v>
+        <v>1.0171</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0218</v>
+        <v>0.8935999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>1.2968</v>
+        <v>1.1611</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.3186</v>
+        <v>-0.2676</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6237</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4244</v>
+        <v>-1.0361</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.326</v>
+        <v>-0.4637</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7503</v>
+        <v>-0.5724</v>
       </c>
       <c r="V5" t="n">
-        <v>3.8945</v>
+        <v>0.1418</v>
       </c>
       <c r="W5" t="n">
-        <v>3.8945</v>
+        <v>0.1418</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. PAPANIKOLAOU</t>
+          <t>S. VEZENKOV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3874</v>
+        <v>0.3869</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4649</v>
+        <v>-0.8612</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8522999999999999</v>
+        <v>1.2481</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0283</v>
+        <v>-1.9722</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2788</v>
+        <v>2.0061</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7495000000000001</v>
+        <v>-3.9783</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1347</v>
+        <v>-0.9504</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1176</v>
+        <v>0.7093</v>
       </c>
       <c r="L6" t="n">
-        <v>1.0171</v>
+        <v>-1.6597</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8935999999999999</v>
+        <v>-1.0218</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1611</v>
+        <v>1.2968</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2676</v>
+        <v>-2.3186</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6959</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0868</v>
+        <v>0.0883</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5816</v>
+        <v>-0.326</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5052</v>
+        <v>0.4143</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1418</v>
+        <v>3.8945</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1418</v>
+        <v>3.8945</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.09810000000000001</v>
+        <v>-0.1885</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7164</v>
+        <v>0.3625</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6182</v>
+        <v>-0.551</v>
       </c>
       <c r="G8" t="n">
         <v>-2.7175</v>
@@ -1078,13 +1078,13 @@
         <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.3872</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2794</v>
+        <v>-0.0745</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3945</v>
+        <v>0.4617</v>
       </c>
       <c r="V8" t="n">
         <v>1.214</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. ANTETOKOUNMPO</t>
+          <t>S. LEE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.374</v>
+        <v>-1.6876</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7065</v>
+        <v>-2.1212</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0805</v>
+        <v>0.4336</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6927</v>
+        <v>-0.7077</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3313</v>
+        <v>-0.9855</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3614</v>
+        <v>0.2777</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1466</v>
+        <v>-0.8398</v>
       </c>
       <c r="K9" t="n">
-        <v>0.521</v>
+        <v>-0.7527</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6257</v>
+        <v>-0.0871</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4539</v>
+        <v>0.1321</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1896</v>
+        <v>-0.2327</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2643</v>
+        <v>0.3648</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9278</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0668</v>
+        <v>-0.284</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7196</v>
+        <v>-0.1217</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7863</v>
+        <v>-0.1623</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. LEE</t>
+          <t>K. ANTETOKOUNMPO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1587</v>
+        <v>-1.8458</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3571</v>
+        <v>0.2346</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1984</v>
+        <v>-2.0805</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7077</v>
+        <v>0.6927</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9855</v>
+        <v>0.3313</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2777</v>
+        <v>0.3614</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8398</v>
+        <v>1.1466</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7527</v>
+        <v>0.521</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0871</v>
+        <v>0.6257</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1321</v>
+        <v>-0.4539</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2327</v>
+        <v>-0.1896</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3648</v>
+        <v>-0.2643</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6959</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7552</v>
+        <v>-0.5386</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3576</v>
+        <v>0.2478</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3976</v>
+        <v>-0.7863</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6877</v>
+        <v>-3.5938</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.3485</v>
+        <v>-4.7587</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6608000000000001</v>
+        <v>1.1649</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3359</v>
@@ -1312,13 +1312,13 @@
         <v>2.0876</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3544</v>
+        <v>-0.2605</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8804</v>
+        <v>-0.2906</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.474</v>
+        <v>0.0301</v>
       </c>
       <c r="V11" t="n">
         <v>0.3943</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.901</v>
+        <v>-5.1369</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1496</v>
+        <v>-3.3855</v>
       </c>
       <c r="F12" t="n">
         <v>-1.7515</v>
@@ -1390,10 +1390,10 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9357</v>
+        <v>0.6998</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2126</v>
+        <v>-0.0233</v>
       </c>
       <c r="U12" t="n">
         <v>0.7231</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.9704999999999986</v>
+        <v>-0.9705000000000021</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.047799999999999</v>
+        <v>-4.047800000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0773</v>
+        <v>3.0771</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6084000000000009</v>
+        <v>0.6084000000000018</v>
       </c>
       <c r="H13" t="n">
         <v>6.915400000000002</v>
@@ -1441,25 +1441,25 @@
         <v>-6.3071</v>
       </c>
       <c r="J13" t="n">
-        <v>4.789199999999999</v>
+        <v>4.789200000000001</v>
       </c>
       <c r="K13" t="n">
         <v>1.595</v>
       </c>
       <c r="L13" t="n">
-        <v>3.1943</v>
+        <v>3.194300000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-4.1808</v>
       </c>
       <c r="N13" t="n">
-        <v>5.320499999999999</v>
+        <v>5.320500000000001</v>
       </c>
       <c r="O13" t="n">
         <v>-9.5015</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.799</v>
+        <v>-5.798999999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-16.2369</v>
@@ -1468,13 +1468,13 @@
         <v>10.4379</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2942999999999999</v>
+        <v>0.2942</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0983</v>
+        <v>-1.0984</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3926</v>
+        <v>1.3927</v>
       </c>
       <c r="V13" t="n">
         <v>3.925499999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.0734</v>
+        <v>7.2693</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9608</v>
+        <v>5.6069</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1126</v>
+        <v>1.6624</v>
       </c>
       <c r="G14" t="n">
         <v>3.1014</v>
@@ -1546,13 +1546,13 @@
         <v>0.9278</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0416</v>
+        <v>1.2375</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9831</v>
+        <v>0.6293</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0584</v>
+        <v>0.6082</v>
       </c>
       <c r="V14" t="n">
         <v>2.0026</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.0696</v>
+        <v>4.341</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5368</v>
+        <v>3.065</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5328</v>
+        <v>1.276</v>
       </c>
       <c r="G15" t="n">
         <v>1.1471</v>
@@ -1624,13 +1624,13 @@
         <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2962</v>
+        <v>1.5676</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2819</v>
+        <v>0.8101</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0144</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>0.9304</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. OSMANI</t>
+          <t>G. PAPAGIANNIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1941</v>
+        <v>1.142</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9943</v>
+        <v>0.5225</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8002</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1583</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3155</v>
+        <v>0.4683</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1573</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1196</v>
+        <v>1.5876</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0657</v>
+        <v>0.3865</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0539</v>
+        <v>1.2011</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9613</v>
+        <v>-1.0256</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2499</v>
+        <v>0.0818</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2112</v>
+        <v>-1.1074</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1419</v>
+        <v>-0.4353</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0351</v>
+        <v>-1.0651</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1067</v>
+        <v>0.6297</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.3558</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. CORDINIER</t>
+          <t>E. OSMANI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1209</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2943</v>
+        <v>1.5225</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1734</v>
+        <v>-0.7437</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1756</v>
+        <v>1.1583</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3253</v>
+        <v>1.3155</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8503</v>
+        <v>-0.1573</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8547</v>
+        <v>2.1196</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8942</v>
+        <v>1.0657</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9606</v>
+        <v>1.0539</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6791</v>
+        <v>-0.9613</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5688</v>
+        <v>0.2499</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1103</v>
+        <v>-1.2112</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3195</v>
+        <v>-0.232</v>
       </c>
       <c r="R17" t="n">
         <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3913</v>
+        <v>-0.5573</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7591</v>
+        <v>-0.507</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6322</v>
+        <v>-0.0503</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.7501</v>
+        <v>-1.214</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.7501</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. PAPAGIANNIS</t>
+          <t>P. DOZIER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7089</v>
+        <v>0.7468</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1687</v>
+        <v>-0.3822</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5402</v>
+        <v>1.129</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5620000000000001</v>
+        <v>-1.5809</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4683</v>
+        <v>-1.2597</v>
       </c>
       <c r="I18" t="n">
-        <v>0.09370000000000001</v>
+        <v>-0.3212</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5876</v>
+        <v>-0.7445000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3865</v>
+        <v>-0.5336</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2011</v>
+        <v>-0.2109</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0256</v>
+        <v>-0.8364</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0818</v>
+        <v>-0.7261</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1074</v>
+        <v>-0.1103</v>
       </c>
       <c r="P18" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8685</v>
+        <v>1.0262</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.4189</v>
+        <v>0.2205</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5505</v>
+        <v>0.8057</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3717</v>
+        <v>0.6577</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0968</v>
+        <v>-0.9788</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4685</v>
+        <v>1.6365</v>
       </c>
       <c r="G19" t="n">
         <v>0.0945</v>
@@ -1936,13 +1936,13 @@
         <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4187</v>
+        <v>-0.1327</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2161</v>
+        <v>-0.0982</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2025</v>
+        <v>-0.0345</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. DOZIER</t>
+          <t>I. CORDINIER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1968</v>
+        <v>0.5268</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.854</v>
+        <v>0.8225</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6572</v>
+        <v>-0.2957</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5809</v>
+        <v>2.1756</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2597</v>
+        <v>0.3253</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3212</v>
+        <v>1.8503</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7445000000000001</v>
+        <v>2.8547</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5336</v>
+        <v>0.8942</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2109</v>
+        <v>1.9606</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8364</v>
+        <v>-0.6791</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7261</v>
+        <v>-0.5688</v>
       </c>
       <c r="O20" t="n">
         <v>-0.1103</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1598</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.7971</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2513</v>
+        <v>0.2873</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3339</v>
+        <v>0.5098</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1418</v>
+        <v>-1.7501</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8369</v>
+        <v>-1.303</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3496</v>
+        <v>-2.9957</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5127</v>
+        <v>1.6928</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7753</v>
@@ -2092,13 +2092,13 @@
         <v>2.7834</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2573</v>
+        <v>-0.7233000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.5604</v>
+        <v>-1.2065</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3031</v>
+        <v>0.4832</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3558</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. SMITS</t>
+          <t>S. LARKIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9851</v>
+        <v>-1.706</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1822</v>
+        <v>-2.7222</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8029</v>
+        <v>1.0162</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5582</v>
+        <v>0.2556</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.15</v>
+        <v>-5.7337</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4082</v>
+        <v>5.9893</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1471</v>
+        <v>1.882</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0504</v>
+        <v>-5.1109</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1975</v>
+        <v>6.9929</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4112</v>
+        <v>-1.6264</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2004</v>
+        <v>-0.6227</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2108</v>
+        <v>-1.0037</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9278</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.3917</v>
+        <v>-4.639</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4639</v>
+        <v>2.3195</v>
       </c>
       <c r="S22" t="n">
-        <v>1.1092</v>
+        <v>-0.7143</v>
       </c>
       <c r="T22" t="n">
-        <v>1.3566</v>
+        <v>-1.0374</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2473</v>
+        <v>0.3231</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.6083</v>
+        <v>1.0722</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. LARKIN</t>
+          <t>R. SMITS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3389</v>
+        <v>-2.8279</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.312</v>
+        <v>-1.1258</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0269</v>
+        <v>-1.7021</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2556</v>
+        <v>-0.5582</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.7337</v>
+        <v>-0.15</v>
       </c>
       <c r="I23" t="n">
-        <v>5.9893</v>
+        <v>-0.4082</v>
       </c>
       <c r="J23" t="n">
-        <v>1.882</v>
+        <v>-0.1471</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.1109</v>
+        <v>0.0504</v>
       </c>
       <c r="L23" t="n">
-        <v>6.9929</v>
+        <v>-0.1975</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6264</v>
+        <v>-0.4112</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6227</v>
+        <v>-0.2004</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0037</v>
+        <v>-0.2108</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.3195</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.639</v>
+        <v>-1.3917</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3195</v>
+        <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.3472</v>
+        <v>0.2664</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.6272</v>
+        <v>0.4129</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.72</v>
+        <v>-0.1465</v>
       </c>
       <c r="V23" t="n">
-        <v>1.0722</v>
+        <v>-1.6083</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.2104</v>
+        <v>-5.5096</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.2374</v>
+        <v>-6.4117</v>
       </c>
       <c r="F24" t="n">
-        <v>0.027</v>
+        <v>0.9021</v>
       </c>
       <c r="G24" t="n">
         <v>-5.1884</v>
@@ -2326,13 +2326,13 @@
         <v>1.6237</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1817</v>
+        <v>0.519</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6642</v>
+        <v>0.1614</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5175</v>
+        <v>0.3576</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9704999999999995</v>
+        <v>4.115800000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.077099999999999</v>
+        <v>-3.076999999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>4.0476</v>
+        <v>7.193000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-0.6082999999999998</v>
@@ -2383,7 +2383,7 @@
         <v>-5.3204</v>
       </c>
       <c r="L25" t="n">
-        <v>9.501399999999999</v>
+        <v>9.5014</v>
       </c>
       <c r="M25" t="n">
         <v>-4.7893</v>
@@ -2392,7 +2392,7 @@
         <v>-1.5947</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.194599999999999</v>
+        <v>-3.1946</v>
       </c>
       <c r="P25" t="n">
         <v>5.799</v>
@@ -2404,13 +2404,13 @@
         <v>16.2368</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2944000000000007</v>
+        <v>2.8509</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.3925</v>
+        <v>-1.3927</v>
       </c>
       <c r="U25" t="n">
-        <v>1.0985</v>
+        <v>4.243600000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-3.9256</v>
